--- a/jpcore-r4/feature/test-claude-opus/observations-summary.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/observations-summary.xlsx
@@ -83,7 +83,7 @@
     <t>null#57133-1</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
     <t>dateTime</t>
